--- a/data/official_data/knowledge/library.xlsx
+++ b/data/official_data/knowledge/library.xlsx
@@ -129,12 +129,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -466,14 +469,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
@@ -483,14 +486,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
@@ -500,7 +503,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -517,7 +520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -534,7 +537,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -551,7 +554,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -568,7 +571,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
